--- a/Interim Analyses/state_retail_summary_prices.xlsx
+++ b/Interim Analyses/state_retail_summary_prices.xlsx
@@ -1150,7 +1150,7 @@
         <v>2025</v>
       </c>
       <c r="D26">
-        <v>35.78563968286084</v>
+        <v>48.62634905448948</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>357.8563968286084</v>
+        <v>486.2634905448948</v>
       </c>
     </row>
     <row r="27">
@@ -1181,7 +1181,7 @@
         <v>2030</v>
       </c>
       <c r="D27">
-        <v>26.30834983338336</v>
+        <v>32.53704007365889</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>263.0834983338336</v>
+        <v>325.370400736589</v>
       </c>
     </row>
     <row r="28">
@@ -1212,7 +1212,7 @@
         <v>2035</v>
       </c>
       <c r="D28">
-        <v>38.32605123465543</v>
+        <v>53.38668630841173</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>383.2605123465543</v>
+        <v>533.8668630841173</v>
       </c>
     </row>
     <row r="29">
@@ -1243,7 +1243,7 @@
         <v>2050</v>
       </c>
       <c r="D29">
-        <v>39.6053310447015</v>
+        <v>55.89687130165465</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>396.053310447015</v>
+        <v>558.9687130165465</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="D30">
-        <v>37.22452121168349</v>
+        <v>47.69469209977621</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>372.2452121168349</v>
+        <v>476.9469209977622</v>
       </c>
     </row>
     <row r="31">
@@ -1305,7 +1305,7 @@
         <v>2030</v>
       </c>
       <c r="D31">
-        <v>33.65447751855878</v>
+        <v>41.43477313122998</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>336.5447751855878</v>
+        <v>414.3477313122998</v>
       </c>
     </row>
     <row r="32">
@@ -1336,7 +1336,7 @@
         <v>2035</v>
       </c>
       <c r="D32">
-        <v>37.39931617268575</v>
+        <v>53.36468950736896</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>373.9931617268575</v>
+        <v>533.6468950736896</v>
       </c>
     </row>
     <row r="33">
@@ -1367,7 +1367,7 @@
         <v>2050</v>
       </c>
       <c r="D33">
-        <v>39.6032469414382</v>
+        <v>57.60792939278572</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>396.032469414382</v>
+        <v>576.0792939278572</v>
       </c>
     </row>
     <row r="34">
@@ -1398,7 +1398,7 @@
         <v>2025</v>
       </c>
       <c r="D34">
-        <v>42.54421136205405</v>
+        <v>55.16090858796075</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>425.4421136205405</v>
+        <v>551.6090858796075</v>
       </c>
     </row>
     <row r="35">
@@ -1429,7 +1429,7 @@
         <v>2030</v>
       </c>
       <c r="D35">
-        <v>36.48165331279021</v>
+        <v>44.64685419997784</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>364.8165331279021</v>
+        <v>446.4685419997784</v>
       </c>
     </row>
     <row r="36">
@@ -1460,7 +1460,7 @@
         <v>2035</v>
       </c>
       <c r="D36">
-        <v>44.34346774489298</v>
+        <v>60.69231937466017</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>443.4346774489298</v>
+        <v>606.9231937466018</v>
       </c>
     </row>
     <row r="37">
@@ -1491,7 +1491,7 @@
         <v>2050</v>
       </c>
       <c r="D37">
-        <v>46.25241510763466</v>
+        <v>64.3219498327538</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>462.5241510763466</v>
+        <v>643.219498327538</v>
       </c>
     </row>
     <row r="38">
@@ -1522,7 +1522,7 @@
         <v>2025</v>
       </c>
       <c r="D38">
-        <v>31.88991684404807</v>
+        <v>46.2112917550506</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>318.8991684404807</v>
+        <v>462.112917550506</v>
       </c>
     </row>
     <row r="39">
@@ -1553,7 +1553,7 @@
         <v>2030</v>
       </c>
       <c r="D39">
-        <v>27.43150849063927</v>
+        <v>36.81923399438863</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>274.3150849063927</v>
+        <v>368.1923399438862</v>
       </c>
     </row>
     <row r="40">
@@ -1584,7 +1584,7 @@
         <v>2035</v>
       </c>
       <c r="D40">
-        <v>32.8795581750469</v>
+        <v>47.25632314106228</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>328.795581750469</v>
+        <v>472.5632314106228</v>
       </c>
     </row>
     <row r="41">
@@ -1615,7 +1615,7 @@
         <v>2050</v>
       </c>
       <c r="D41">
-        <v>35.81603813804526</v>
+        <v>53.51824989169766</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>358.1603813804526</v>
+        <v>535.1824989169766</v>
       </c>
     </row>
     <row r="42">
@@ -1646,7 +1646,7 @@
         <v>2025</v>
       </c>
       <c r="D42">
-        <v>32.68779158657987</v>
+        <v>42.51287234438387</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>326.8779158657987</v>
+        <v>425.1287234438387</v>
       </c>
     </row>
     <row r="43">
@@ -1677,7 +1677,7 @@
         <v>2030</v>
       </c>
       <c r="D43">
-        <v>34.56549140322803</v>
+        <v>47.94913235376639</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>345.6549140322803</v>
+        <v>479.4913235376639</v>
       </c>
     </row>
     <row r="44">
@@ -1708,7 +1708,7 @@
         <v>2035</v>
       </c>
       <c r="D44">
-        <v>33.37337393648825</v>
+        <v>45.8583784755437</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>333.7337393648825</v>
+        <v>458.5837847554369</v>
       </c>
     </row>
     <row r="45">
@@ -1739,7 +1739,7 @@
         <v>2050</v>
       </c>
       <c r="D45">
-        <v>35.17556591891587</v>
+        <v>49.41438642572923</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>351.7556591891587</v>
+        <v>494.1438642572924</v>
       </c>
     </row>
     <row r="46">
@@ -1770,7 +1770,7 @@
         <v>2025</v>
       </c>
       <c r="D46">
-        <v>15.39534075781565</v>
+        <v>29.28501786688318</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>153.9534075781565</v>
+        <v>292.8501786688319</v>
       </c>
     </row>
     <row r="47">
@@ -1801,7 +1801,7 @@
         <v>2030</v>
       </c>
       <c r="D47">
-        <v>18.7813030222434</v>
+        <v>18.52769058852098</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>187.813030222434</v>
+        <v>185.2769058852098</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
         <v>2035</v>
       </c>
       <c r="D48">
-        <v>26.38500451556178</v>
+        <v>34.57861957165631</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>263.8500451556177</v>
+        <v>345.7861957165631</v>
       </c>
     </row>
     <row r="49">
@@ -1863,7 +1863,7 @@
         <v>2050</v>
       </c>
       <c r="D49">
-        <v>34.35614651994054</v>
+        <v>37.89347034606737</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>343.5614651994054</v>
+        <v>378.9347034606736</v>
       </c>
     </row>
     <row r="50">
@@ -1925,7 +1925,7 @@
         <v>2025</v>
       </c>
       <c r="D51">
-        <v>38.00332405686318</v>
+        <v>53.13039181039171</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>380.0332405686318</v>
+        <v>531.3039181039171</v>
       </c>
     </row>
     <row r="52">
@@ -1987,7 +1987,7 @@
         <v>2030</v>
       </c>
       <c r="D53">
-        <v>34.78920436701694</v>
+        <v>42.52074763323893</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>347.8920436701694</v>
+        <v>425.2074763323893</v>
       </c>
     </row>
     <row r="54">
@@ -2049,7 +2049,7 @@
         <v>2035</v>
       </c>
       <c r="D55">
-        <v>41.31514528397451</v>
+        <v>57.8273138498709</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="G55">
-        <v>413.1514528397451</v>
+        <v>578.2731384987089</v>
       </c>
     </row>
     <row r="56">
@@ -2111,7 +2111,7 @@
         <v>2050</v>
       </c>
       <c r="D57">
-        <v>42.02182401770059</v>
+        <v>59.839511794298</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="G57">
-        <v>420.2182401770059</v>
+        <v>598.3951179429799</v>
       </c>
     </row>
   </sheetData>
